--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3726</v>
+        <v>3729</v>
       </c>
       <c r="O16" t="n">
-        <v>3726</v>
+        <v>3729</v>
       </c>
       <c r="R16" t="n">
-        <v>13.68489683953074</v>
+        <v>13.6959152749893</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3427</v>
+        <v>3477</v>
       </c>
       <c r="O25" t="n">
-        <v>3427</v>
+        <v>3477</v>
       </c>
       <c r="R25" t="n">
-        <v>12.58672610549432</v>
+        <v>12.77036669647031</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40057</v>
+        <v>40110</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3729</v>
+        <v>3730</v>
       </c>
       <c r="O16" t="n">
-        <v>3729</v>
+        <v>3730</v>
       </c>
       <c r="R16" t="n">
-        <v>13.6959152749893</v>
+        <v>13.69958808680882</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3477</v>
+        <v>3491</v>
       </c>
       <c r="O25" t="n">
-        <v>3477</v>
+        <v>3491</v>
       </c>
       <c r="R25" t="n">
-        <v>12.77036669647031</v>
+        <v>12.82178606194359</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40110</v>
+        <v>40125</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3730</v>
+        <v>3734</v>
       </c>
       <c r="O16" t="n">
-        <v>3730</v>
+        <v>3734</v>
       </c>
       <c r="R16" t="n">
-        <v>13.69958808680882</v>
+        <v>13.7142793340869</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3491</v>
+        <v>3502</v>
       </c>
       <c r="O25" t="n">
-        <v>3491</v>
+        <v>3502</v>
       </c>
       <c r="R25" t="n">
-        <v>12.82178606194359</v>
+        <v>12.86218699195831</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40125</v>
+        <v>40140</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3734</v>
+        <v>3736</v>
       </c>
       <c r="O16" t="n">
-        <v>3734</v>
+        <v>3736</v>
       </c>
       <c r="R16" t="n">
-        <v>13.7142793340869</v>
+        <v>13.72162495772594</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="O25" t="n">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="R25" t="n">
-        <v>12.86218699195831</v>
+        <v>12.85851418013878</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40140</v>
+        <v>40141</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3736</v>
+        <v>3739</v>
       </c>
       <c r="O16" t="n">
-        <v>3736</v>
+        <v>3739</v>
       </c>
       <c r="R16" t="n">
-        <v>13.72162495772594</v>
+        <v>13.73264339318449</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3501</v>
+        <v>3519</v>
       </c>
       <c r="O25" t="n">
-        <v>3501</v>
+        <v>3519</v>
       </c>
       <c r="R25" t="n">
-        <v>12.85851418013878</v>
+        <v>12.92462479289014</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40141</v>
+        <v>40162</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="O25" t="n">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="R25" t="n">
-        <v>12.92462479289014</v>
+        <v>12.92095198107062</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40162</v>
+        <v>40161</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3518</v>
+        <v>3549</v>
       </c>
       <c r="O25" t="n">
-        <v>3518</v>
+        <v>3549</v>
       </c>
       <c r="R25" t="n">
-        <v>12.92095198107062</v>
+        <v>13.03480914747573</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40161</v>
+        <v>40192</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3739</v>
+        <v>3740</v>
       </c>
       <c r="O16" t="n">
-        <v>3739</v>
+        <v>3740</v>
       </c>
       <c r="R16" t="n">
-        <v>13.73264339318449</v>
+        <v>13.73631620500402</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3549</v>
+        <v>3551</v>
       </c>
       <c r="O25" t="n">
-        <v>3549</v>
+        <v>3551</v>
       </c>
       <c r="R25" t="n">
-        <v>13.03480914747573</v>
+        <v>13.04215477111478</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40192</v>
+        <v>40195</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3740</v>
+        <v>3742</v>
       </c>
       <c r="O16" t="n">
-        <v>3740</v>
+        <v>3742</v>
       </c>
       <c r="R16" t="n">
-        <v>13.73631620500402</v>
+        <v>13.74366182864305</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3551</v>
+        <v>3563</v>
       </c>
       <c r="O25" t="n">
-        <v>3551</v>
+        <v>3563</v>
       </c>
       <c r="R25" t="n">
-        <v>13.04215477111478</v>
+        <v>13.08622851294901</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40195</v>
+        <v>40209</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -5337,13 +5337,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>141</v>
+        <v>3198</v>
       </c>
       <c r="O34" t="n">
-        <v>141</v>
+        <v>3198</v>
       </c>
       <c r="R34" t="n">
-        <v>0.5178664665522904</v>
+        <v>11.74565219882429</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40209</v>
+        <v>43266</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -5337,13 +5337,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3198</v>
+        <v>3293</v>
       </c>
       <c r="O34" t="n">
-        <v>3198</v>
+        <v>3293</v>
       </c>
       <c r="R34" t="n">
-        <v>11.74565219882429</v>
+        <v>12.09456932167867</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43266</v>
+        <v>43361</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -869,12 +869,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -899,29 +899,26 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3599</v>
+        <v>42</v>
       </c>
       <c r="O3" t="n">
-        <v>3599</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R3" t="n">
-        <v>13.21844973845173</v>
+        <v>8.577240089203297</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -955,12 +952,12 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -975,12 +972,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1017,12 +1014,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1047,29 +1044,26 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3965</v>
+        <v>1202</v>
       </c>
       <c r="O4" t="n">
-        <v>3965</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="R4" t="n">
-        <v>14.56269886439597</v>
+        <v>13.86373060072514</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1103,12 +1097,12 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1123,12 +1117,12 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1165,12 +1159,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1195,26 +1189,26 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3781</v>
+        <v>198</v>
       </c>
       <c r="O5" t="n">
-        <v>3781</v>
+        <v>198</v>
       </c>
       <c r="R5" t="n">
-        <v>13.88690148960433</v>
+        <v>73.63359476978344</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1248,12 +1242,12 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1268,12 +1262,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -1310,12 +1304,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1340,26 +1334,26 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3664</v>
+        <v>662</v>
       </c>
       <c r="O6" t="n">
-        <v>3664</v>
+        <v>662</v>
       </c>
       <c r="R6" t="n">
-        <v>13.45718250672051</v>
+        <v>11.53418413331844</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1393,12 +1387,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1413,12 +1407,12 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -1455,12 +1449,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1485,26 +1479,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3637</v>
+        <v>196</v>
       </c>
       <c r="O7" t="n">
-        <v>3637</v>
+        <v>196</v>
       </c>
       <c r="R7" t="n">
-        <v>13.35801658759348</v>
+        <v>10.22518358378077</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1538,12 +1532,12 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1558,12 +1552,12 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -1600,12 +1594,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1630,23 +1624,26 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="O8" t="n">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.96079842807965</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1680,7 +1677,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1700,7 +1697,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -1742,12 +1739,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1772,23 +1769,26 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1123</v>
+        <v>922</v>
       </c>
       <c r="O9" t="n">
-        <v>1123</v>
+        <v>922</v>
+      </c>
+      <c r="R9" t="n">
+        <v>12.88749676589527</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1914,23 +1914,26 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>199</v>
+        <v>601</v>
       </c>
       <c r="O10" t="n">
-        <v>199</v>
+        <v>601</v>
+      </c>
+      <c r="R10" t="n">
+        <v>19.41075284653362</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1964,7 +1967,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1984,7 +1987,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2026,12 +2029,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2056,23 +2059,29 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>655</v>
+        <v>3599</v>
       </c>
       <c r="O11" t="n">
-        <v>655</v>
+        <v>3599</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>13.21844973845173</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2106,12 +2115,12 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2126,12 +2135,12 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -2168,12 +2177,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2198,23 +2207,26 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>207</v>
+        <v>37</v>
       </c>
       <c r="O12" t="n">
-        <v>207</v>
+        <v>37</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7.556140078583856</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2248,7 +2260,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -2268,7 +2280,7 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -2310,12 +2322,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2340,23 +2352,26 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>1078</v>
       </c>
       <c r="O13" t="n">
-        <v>26</v>
+        <v>1078</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12.43352877502637</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2390,7 +2405,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -2410,7 +2425,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -2452,12 +2467,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2482,23 +2497,26 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>923</v>
+        <v>221</v>
       </c>
       <c r="O14" t="n">
-        <v>923</v>
+        <v>221</v>
+      </c>
+      <c r="R14" t="n">
+        <v>82.18699214203102</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2532,7 +2550,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2552,7 +2570,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -2594,12 +2612,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2624,23 +2642,26 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>475</v>
+        <v>649</v>
       </c>
       <c r="O15" t="n">
-        <v>475</v>
+        <v>649</v>
+      </c>
+      <c r="R15" t="n">
+        <v>11.30768202798137</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2674,7 +2695,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2694,7 +2715,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -2736,12 +2757,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2766,26 +2787,26 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3742</v>
+        <v>222</v>
       </c>
       <c r="O16" t="n">
-        <v>3742</v>
+        <v>222</v>
       </c>
       <c r="R16" t="n">
-        <v>13.74366182864305</v>
+        <v>11.58158548775169</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2819,12 +2840,12 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2839,12 +2860,12 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -2881,12 +2902,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2911,23 +2932,26 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>14</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.410920782309352</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2961,7 +2985,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2981,7 +3005,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -3023,12 +3047,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3053,23 +3077,26 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1212</v>
+        <v>945</v>
       </c>
       <c r="O18" t="n">
-        <v>1212</v>
+        <v>945</v>
+      </c>
+      <c r="R18" t="n">
+        <v>13.2089852969317</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3103,7 +3130,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -3123,7 +3150,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -3165,12 +3192,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3195,23 +3222,26 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>171</v>
+        <v>453</v>
       </c>
       <c r="O19" t="n">
-        <v>171</v>
+        <v>453</v>
+      </c>
+      <c r="R19" t="n">
+        <v>14.63073384272833</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3245,7 +3275,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -3265,7 +3295,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -3307,12 +3337,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3337,23 +3367,29 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>683</v>
+        <v>3965</v>
       </c>
       <c r="O20" t="n">
-        <v>683</v>
+        <v>3965</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>14.56269886439597</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3387,12 +3423,12 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3407,12 +3443,12 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -3449,12 +3485,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3479,23 +3515,26 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>186</v>
+        <v>39</v>
       </c>
       <c r="O21" t="n">
-        <v>186</v>
+        <v>39</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7.964580082831633</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3529,7 +3568,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -3549,7 +3588,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -3591,12 +3630,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3621,23 +3660,26 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>18</v>
+        <v>1228</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>1228</v>
+      </c>
+      <c r="R22" t="n">
+        <v>14.16361162869423</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3671,7 +3713,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -3691,7 +3733,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -3733,12 +3775,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3763,23 +3805,26 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>924</v>
+        <v>206</v>
       </c>
       <c r="O23" t="n">
-        <v>924</v>
+        <v>206</v>
+      </c>
+      <c r="R23" t="n">
+        <v>76.60868950795651</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3813,7 +3858,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3833,7 +3878,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -3875,12 +3920,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3905,23 +3950,26 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>479</v>
+        <v>671</v>
       </c>
       <c r="O24" t="n">
-        <v>479</v>
+        <v>671</v>
+      </c>
+      <c r="R24" t="n">
+        <v>11.69099328316718</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3955,7 +4003,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3975,7 +4023,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -4017,12 +4065,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4047,26 +4095,26 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3563</v>
+        <v>215</v>
       </c>
       <c r="O25" t="n">
-        <v>3563</v>
+        <v>215</v>
       </c>
       <c r="R25" t="n">
-        <v>13.08622851294901</v>
+        <v>11.21640035975952</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4100,12 +4148,12 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4120,12 +4168,12 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -4162,12 +4210,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4192,23 +4240,26 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O26" t="n">
-        <v>32</v>
+        <v>25</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4.305215682695271</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4242,7 +4293,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -4262,7 +4313,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -4304,12 +4355,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4334,23 +4385,26 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="O27" t="n">
-        <v>993</v>
+        <v>1001</v>
+      </c>
+      <c r="R27" t="n">
+        <v>13.99173998119432</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4384,7 +4438,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -4404,7 +4458,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -4446,12 +4500,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4476,23 +4530,26 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>75</v>
+        <v>597</v>
       </c>
       <c r="O28" t="n">
-        <v>75</v>
+        <v>597</v>
+      </c>
+      <c r="R28" t="n">
+        <v>19.28156314372806</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4526,7 +4583,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -4546,7 +4603,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -4588,12 +4645,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4618,23 +4675,26 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>560</v>
+        <v>3781</v>
       </c>
       <c r="O29" t="n">
-        <v>560</v>
+        <v>3781</v>
+      </c>
+      <c r="R29" t="n">
+        <v>13.88690148960433</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4668,12 +4728,12 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4688,12 +4748,12 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -4730,12 +4790,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4760,23 +4820,26 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>169</v>
+        <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>169</v>
+        <v>30</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6.126600063716641</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4810,7 +4873,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -4830,7 +4893,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -4872,12 +4935,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4902,23 +4965,26 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>22</v>
+        <v>1155</v>
       </c>
       <c r="O31" t="n">
-        <v>22</v>
+        <v>1155</v>
+      </c>
+      <c r="R31" t="n">
+        <v>13.32163797324254</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4952,7 +5018,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -4972,7 +5038,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -5014,12 +5080,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5044,23 +5110,26 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>674</v>
+        <v>208</v>
       </c>
       <c r="O32" t="n">
-        <v>674</v>
+        <v>208</v>
+      </c>
+      <c r="R32" t="n">
+        <v>77.35246319249978</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5094,7 +5163,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -5114,7 +5183,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -5156,12 +5225,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5186,23 +5255,26 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>410</v>
+        <v>664</v>
       </c>
       <c r="O33" t="n">
-        <v>410</v>
+        <v>664</v>
+      </c>
+      <c r="R33" t="n">
+        <v>11.56903061106261</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5236,7 +5308,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -5256,7 +5328,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -5298,12 +5370,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5328,26 +5400,26 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3293</v>
+        <v>225</v>
       </c>
       <c r="O34" t="n">
-        <v>3293</v>
+        <v>225</v>
       </c>
       <c r="R34" t="n">
-        <v>12.09456932167867</v>
+        <v>11.73809339974833</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5381,35 +5453,6995 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>11</v>
+      </c>
+      <c r="O35" t="n">
+        <v>11</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.89429490038592</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>956</v>
+      </c>
+      <c r="O36" t="n">
+        <v>956</v>
+      </c>
+      <c r="R36" t="n">
+        <v>13.36274068134043</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>532</v>
+      </c>
+      <c r="O37" t="n">
+        <v>532</v>
+      </c>
+      <c r="R37" t="n">
+        <v>17.18223047313791</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>3664</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3664</v>
+      </c>
+      <c r="R38" t="n">
+        <v>13.45718250672051</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA34" t="inlineStr">
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB34" t="inlineStr">
+      <c r="BB38" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>31</v>
+      </c>
+      <c r="O39" t="n">
+        <v>31</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6.330820065840528</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1217</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1217</v>
+      </c>
+      <c r="R40" t="n">
+        <v>14.03673888609192</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>203</v>
+      </c>
+      <c r="O41" t="n">
+        <v>203</v>
+      </c>
+      <c r="R41" t="n">
+        <v>75.49302898114162</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>627</v>
+      </c>
+      <c r="O42" t="n">
+        <v>627</v>
+      </c>
+      <c r="R42" t="n">
+        <v>10.92437077279556</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>199</v>
+      </c>
+      <c r="O43" t="n">
+        <v>199</v>
+      </c>
+      <c r="R43" t="n">
+        <v>10.38169149577742</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>19</v>
+      </c>
+      <c r="O44" t="n">
+        <v>19</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3.271963918848407</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>911</v>
+      </c>
+      <c r="O45" t="n">
+        <v>911</v>
+      </c>
+      <c r="R45" t="n">
+        <v>12.73374138148654</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>463</v>
+      </c>
+      <c r="O46" t="n">
+        <v>463</v>
+      </c>
+      <c r="R46" t="n">
+        <v>14.9537080997422</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>3637</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3637</v>
+      </c>
+      <c r="R47" t="n">
+        <v>13.35801658759348</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>29</v>
+      </c>
+      <c r="O48" t="n">
+        <v>29</v>
+      </c>
+      <c r="R48" t="n">
+        <v>5.922380061592753</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>1123</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1123</v>
+      </c>
+      <c r="R49" t="n">
+        <v>12.95255363112673</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>198</v>
+      </c>
+      <c r="O50" t="n">
+        <v>198</v>
+      </c>
+      <c r="R50" t="n">
+        <v>73.63359476978344</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>655</v>
+      </c>
+      <c r="O51" t="n">
+        <v>655</v>
+      </c>
+      <c r="R51" t="n">
+        <v>11.41222146121387</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>208</v>
+      </c>
+      <c r="O52" t="n">
+        <v>208</v>
+      </c>
+      <c r="R52" t="n">
+        <v>10.85121523176735</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>26</v>
+      </c>
+      <c r="O53" t="n">
+        <v>26</v>
+      </c>
+      <c r="R53" t="n">
+        <v>4.477424310003082</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>925</v>
+      </c>
+      <c r="O54" t="n">
+        <v>925</v>
+      </c>
+      <c r="R54" t="n">
+        <v>12.92943005255219</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>476</v>
+      </c>
+      <c r="O55" t="n">
+        <v>476</v>
+      </c>
+      <c r="R55" t="n">
+        <v>15.37357463386023</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>3742</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3742</v>
+      </c>
+      <c r="R56" t="n">
+        <v>13.74366182864305</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>28</v>
+      </c>
+      <c r="O57" t="n">
+        <v>28</v>
+      </c>
+      <c r="R57" t="n">
+        <v>5.718160059468865</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1212</v>
+      </c>
+      <c r="R58" t="n">
+        <v>13.97906945763633</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>205</v>
+      </c>
+      <c r="O59" t="n">
+        <v>205</v>
+      </c>
+      <c r="R59" t="n">
+        <v>76.23680266568489</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>684</v>
+      </c>
+      <c r="O60" t="n">
+        <v>684</v>
+      </c>
+      <c r="R60" t="n">
+        <v>11.91749538850425</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>186</v>
+      </c>
+      <c r="O61" t="n">
+        <v>186</v>
+      </c>
+      <c r="R61" t="n">
+        <v>9.703490543791956</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>19</v>
+      </c>
+      <c r="O62" t="n">
+        <v>19</v>
+      </c>
+      <c r="R62" t="n">
+        <v>3.271963918848407</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>925</v>
+      </c>
+      <c r="O63" t="n">
+        <v>925</v>
+      </c>
+      <c r="R63" t="n">
+        <v>12.92943005255219</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>482</v>
+      </c>
+      <c r="O64" t="n">
+        <v>482</v>
+      </c>
+      <c r="R64" t="n">
+        <v>15.56735918806855</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>3564</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3564</v>
+      </c>
+      <c r="R65" t="n">
+        <v>13.08990132476853</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>34</v>
+      </c>
+      <c r="O66" t="n">
+        <v>34</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6.943480072212192</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1118</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1118</v>
+      </c>
+      <c r="R67" t="n">
+        <v>12.89488420267113</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>165</v>
+      </c>
+      <c r="O68" t="n">
+        <v>165</v>
+      </c>
+      <c r="R68" t="n">
+        <v>61.36132897481954</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>624</v>
+      </c>
+      <c r="O69" t="n">
+        <v>624</v>
+      </c>
+      <c r="R69" t="n">
+        <v>10.87210105617932</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>196</v>
+      </c>
+      <c r="O70" t="n">
+        <v>196</v>
+      </c>
+      <c r="R70" t="n">
+        <v>10.22518358378077</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>26</v>
+      </c>
+      <c r="O71" t="n">
+        <v>26</v>
+      </c>
+      <c r="R71" t="n">
+        <v>4.477424310003082</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>881</v>
+      </c>
+      <c r="O72" t="n">
+        <v>881</v>
+      </c>
+      <c r="R72" t="n">
+        <v>12.31440851491728</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>519</v>
+      </c>
+      <c r="O73" t="n">
+        <v>519</v>
+      </c>
+      <c r="R73" t="n">
+        <v>16.76236393901988</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>3329</v>
+      </c>
+      <c r="O74" t="n">
+        <v>3329</v>
+      </c>
+      <c r="R74" t="n">
+        <v>12.22679054718138</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>27</v>
+      </c>
+      <c r="O75" t="n">
+        <v>27</v>
+      </c>
+      <c r="R75" t="n">
+        <v>5.513940057344977</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>1052</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1052</v>
+      </c>
+      <c r="R76" t="n">
+        <v>12.13364774705727</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>89</v>
+      </c>
+      <c r="O77" t="n">
+        <v>89</v>
+      </c>
+      <c r="R77" t="n">
+        <v>33.09792896217539</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>648</v>
+      </c>
+      <c r="O78" t="n">
+        <v>648</v>
+      </c>
+      <c r="R78" t="n">
+        <v>11.29025878910929</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>165</v>
+      </c>
+      <c r="O79" t="n">
+        <v>165</v>
+      </c>
+      <c r="R79" t="n">
+        <v>8.607935159815446</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>32</v>
+      </c>
+      <c r="O80" t="n">
+        <v>32</v>
+      </c>
+      <c r="R80" t="n">
+        <v>5.510676073849948</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>816</v>
+      </c>
+      <c r="O81" t="n">
+        <v>816</v>
+      </c>
+      <c r="R81" t="n">
+        <v>11.40585397068388</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>464</v>
+      </c>
+      <c r="O82" t="n">
+        <v>464</v>
+      </c>
+      <c r="R82" t="n">
+        <v>14.98600552544359</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -5531,7 +12563,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -5541,7 +12573,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -5593,7 +12625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43361</v>
+        <v>66260</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2084,6 +2129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2229,6 +2279,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2374,6 +2429,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2519,6 +2579,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2664,6 +2729,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2809,6 +2879,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2954,6 +3029,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3099,6 +3179,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3244,6 +3329,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3392,6 +3482,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3537,6 +3632,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3682,6 +3782,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3827,6 +3932,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3972,6 +4082,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4117,6 +4232,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4262,6 +4382,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4407,6 +4532,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4552,6 +4682,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4697,6 +4832,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4842,6 +4982,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4987,6 +5132,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5132,6 +5282,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5277,6 +5432,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5422,6 +5582,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5567,6 +5732,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5712,6 +5882,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5857,6 +6032,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6002,6 +6182,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6147,6 +6332,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6292,6 +6482,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6437,6 +6632,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6582,6 +6782,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6727,6 +6932,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6872,6 +7082,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7017,6 +7232,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7162,6 +7382,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7307,6 +7532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7452,6 +7682,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7597,6 +7832,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7742,6 +7982,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7887,6 +8132,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8032,6 +8282,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8177,6 +8432,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8322,6 +8582,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8467,6 +8732,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8612,6 +8882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8757,6 +9032,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8902,6 +9182,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9047,6 +9332,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9192,6 +9482,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9337,6 +9632,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9482,6 +9782,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9627,6 +9932,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9772,6 +10082,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9904,17 +10219,22 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3564</v>
+        <v>3578</v>
       </c>
       <c r="O65" t="n">
-        <v>3564</v>
+        <v>3578</v>
       </c>
       <c r="R65" t="n">
-        <v>13.08990132476853</v>
+        <v>13.14132069024181</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10062,6 +10382,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10207,6 +10532,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10352,6 +10682,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10497,6 +10832,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10642,6 +10982,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10787,6 +11132,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10932,6 +11282,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11077,6 +11432,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11209,17 +11569,22 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3329</v>
+        <v>3370</v>
       </c>
       <c r="O74" t="n">
-        <v>3329</v>
+        <v>3370</v>
       </c>
       <c r="R74" t="n">
-        <v>12.22679054718138</v>
+        <v>12.37737583178169</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -11367,6 +11732,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11512,6 +11882,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11657,6 +12032,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11802,6 +12182,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11947,6 +12332,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12092,6 +12482,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12237,6 +12632,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12380,6 +12780,11 @@
       <c r="S82" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12625,7 +13030,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66260</v>
+        <v>66315</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -10219,13 +10219,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3578</v>
+        <v>3580</v>
       </c>
       <c r="O65" t="n">
-        <v>3578</v>
+        <v>3580</v>
       </c>
       <c r="R65" t="n">
-        <v>13.14132069024181</v>
+        <v>13.14866631388085</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -11569,13 +11569,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3370</v>
+        <v>3368</v>
       </c>
       <c r="O74" t="n">
-        <v>3370</v>
+        <v>3368</v>
       </c>
       <c r="R74" t="n">
-        <v>12.37737583178169</v>
+        <v>12.37003020814265</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -10219,13 +10219,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="O65" t="n">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="R65" t="n">
-        <v>13.14866631388085</v>
+        <v>13.14499350206133</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -11569,13 +11569,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3368</v>
+        <v>3373</v>
       </c>
       <c r="O74" t="n">
-        <v>3368</v>
+        <v>3373</v>
       </c>
       <c r="R74" t="n">
-        <v>12.37003020814265</v>
+        <v>12.38839426724025</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66315</v>
+        <v>66319</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -10219,13 +10219,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3579</v>
+        <v>3580</v>
       </c>
       <c r="O65" t="n">
-        <v>3579</v>
+        <v>3580</v>
       </c>
       <c r="R65" t="n">
-        <v>13.14499350206133</v>
+        <v>13.14866631388085</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -11569,13 +11569,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3373</v>
+        <v>3378</v>
       </c>
       <c r="O74" t="n">
-        <v>3373</v>
+        <v>3378</v>
       </c>
       <c r="R74" t="n">
-        <v>12.38839426724025</v>
+        <v>12.40675832633785</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66319</v>
+        <v>66325</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>14.11828863423407</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,23 +783,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>8.577240089203297</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,23 +918,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
@@ -1071,11 +1041,6 @@
       <c r="R4" t="n">
         <v>13.86373060072514</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1088,23 +1053,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
@@ -1221,11 +1176,6 @@
       <c r="R5" t="n">
         <v>73.63359476978344</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1238,23 +1188,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1371,11 +1311,6 @@
       <c r="R6" t="n">
         <v>11.53418413331844</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1388,23 +1323,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
@@ -1521,11 +1446,6 @@
       <c r="R7" t="n">
         <v>10.22518358378077</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1538,23 +1458,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
@@ -1671,11 +1581,6 @@
       <c r="R8" t="n">
         <v>3.96079842807965</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1688,23 +1593,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
@@ -1821,11 +1716,6 @@
       <c r="R9" t="n">
         <v>12.88749676589527</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1838,23 +1728,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
@@ -1971,11 +1851,6 @@
       <c r="R10" t="n">
         <v>19.41075284653362</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1988,23 +1863,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>all</t>
@@ -2124,11 +1989,6 @@
       <c r="R11" t="n">
         <v>13.21844973845173</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2141,23 +2001,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>all</t>
@@ -2274,11 +2124,6 @@
       <c r="R12" t="n">
         <v>7.556140078583856</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2291,23 +2136,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2424,11 +2259,6 @@
       <c r="R13" t="n">
         <v>12.43352877502637</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2441,23 +2271,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2574,11 +2394,6 @@
       <c r="R14" t="n">
         <v>82.18699214203102</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2591,23 +2406,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2724,11 +2529,6 @@
       <c r="R15" t="n">
         <v>11.30768202798137</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2741,23 +2541,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2874,11 +2664,6 @@
       <c r="R16" t="n">
         <v>11.58158548775169</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2891,23 +2676,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -3024,11 +2799,6 @@
       <c r="R17" t="n">
         <v>2.410920782309352</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3041,23 +2811,13 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -3174,11 +2934,6 @@
       <c r="R18" t="n">
         <v>13.2089852969317</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3191,23 +2946,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -3324,11 +3069,6 @@
       <c r="R19" t="n">
         <v>14.63073384272833</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3341,23 +3081,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -3477,11 +3207,6 @@
       <c r="R20" t="n">
         <v>14.56269886439597</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3494,23 +3219,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3627,11 +3342,6 @@
       <c r="R21" t="n">
         <v>7.964580082831633</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3644,23 +3354,13 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3777,11 +3477,6 @@
       <c r="R22" t="n">
         <v>14.16361162869423</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3794,23 +3489,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3927,11 +3612,6 @@
       <c r="R23" t="n">
         <v>76.60868950795651</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3944,23 +3624,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -4077,11 +3747,6 @@
       <c r="R24" t="n">
         <v>11.69099328316718</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4094,23 +3759,13 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -4227,11 +3882,6 @@
       <c r="R25" t="n">
         <v>11.21640035975952</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4244,23 +3894,13 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -4377,11 +4017,6 @@
       <c r="R26" t="n">
         <v>4.305215682695271</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4394,23 +4029,13 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -4527,11 +4152,6 @@
       <c r="R27" t="n">
         <v>13.99173998119432</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4544,23 +4164,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -4677,11 +4287,6 @@
       <c r="R28" t="n">
         <v>19.28156314372806</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4694,23 +4299,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4827,11 +4422,6 @@
       <c r="R29" t="n">
         <v>13.88690148960433</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4844,23 +4434,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4977,11 +4557,6 @@
       <c r="R30" t="n">
         <v>6.126600063716641</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4994,23 +4569,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>all</t>
@@ -5127,11 +4692,6 @@
       <c r="R31" t="n">
         <v>13.32163797324254</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5144,23 +4704,13 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>all</t>
@@ -5277,11 +4827,6 @@
       <c r="R32" t="n">
         <v>77.35246319249978</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5294,23 +4839,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -5427,11 +4962,6 @@
       <c r="R33" t="n">
         <v>11.56903061106261</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5444,23 +4974,13 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -5577,11 +5097,6 @@
       <c r="R34" t="n">
         <v>11.73809339974833</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5594,23 +5109,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -5727,11 +5232,6 @@
       <c r="R35" t="n">
         <v>1.89429490038592</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5744,23 +5244,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -5877,11 +5367,6 @@
       <c r="R36" t="n">
         <v>13.36274068134043</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5894,23 +5379,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -6027,11 +5502,6 @@
       <c r="R37" t="n">
         <v>17.18223047313791</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6044,23 +5514,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -6177,11 +5637,6 @@
       <c r="R38" t="n">
         <v>13.45718250672051</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6194,23 +5649,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -6327,11 +5772,6 @@
       <c r="R39" t="n">
         <v>6.330820065840528</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6344,23 +5784,13 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -6477,11 +5907,6 @@
       <c r="R40" t="n">
         <v>14.03673888609192</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6494,23 +5919,13 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -6627,11 +6042,6 @@
       <c r="R41" t="n">
         <v>75.49302898114162</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6644,23 +6054,13 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -6777,11 +6177,6 @@
       <c r="R42" t="n">
         <v>10.92437077279556</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6794,23 +6189,13 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -6927,11 +6312,6 @@
       <c r="R43" t="n">
         <v>10.38169149577742</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6944,23 +6324,13 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>all</t>
@@ -7077,11 +6447,6 @@
       <c r="R44" t="n">
         <v>3.271963918848407</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7094,23 +6459,13 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>all</t>
@@ -7227,11 +6582,6 @@
       <c r="R45" t="n">
         <v>12.73374138148654</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7244,23 +6594,13 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>all</t>
@@ -7377,11 +6717,6 @@
       <c r="R46" t="n">
         <v>14.9537080997422</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7394,23 +6729,13 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>all</t>
@@ -7527,11 +6852,6 @@
       <c r="R47" t="n">
         <v>13.35801658759348</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7544,23 +6864,13 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>all</t>
@@ -7677,11 +6987,6 @@
       <c r="R48" t="n">
         <v>5.922380061592753</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7694,23 +6999,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>all</t>
@@ -7827,11 +7122,6 @@
       <c r="R49" t="n">
         <v>12.95255363112673</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7844,23 +7134,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>all</t>
@@ -7977,11 +7257,6 @@
       <c r="R50" t="n">
         <v>73.63359476978344</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7994,23 +7269,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
@@ -8127,11 +7392,6 @@
       <c r="R51" t="n">
         <v>11.41222146121387</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8144,23 +7404,13 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>all</t>
@@ -8277,11 +7527,6 @@
       <c r="R52" t="n">
         <v>10.85121523176735</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8294,23 +7539,13 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>all</t>
@@ -8427,11 +7662,6 @@
       <c r="R53" t="n">
         <v>4.477424310003082</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8444,23 +7674,13 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>all</t>
@@ -8577,11 +7797,6 @@
       <c r="R54" t="n">
         <v>12.92943005255219</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8594,23 +7809,13 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -8727,11 +7932,6 @@
       <c r="R55" t="n">
         <v>15.37357463386023</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8744,23 +7944,13 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -8877,11 +8067,6 @@
       <c r="R56" t="n">
         <v>13.74366182864305</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8894,23 +8079,13 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -9027,11 +8202,6 @@
       <c r="R57" t="n">
         <v>5.718160059468865</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9044,23 +8214,13 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -9177,11 +8337,6 @@
       <c r="R58" t="n">
         <v>13.97906945763633</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9194,23 +8349,13 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>all</t>
@@ -9327,11 +8472,6 @@
       <c r="R59" t="n">
         <v>76.23680266568489</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9344,23 +8484,13 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>all</t>
@@ -9477,11 +8607,6 @@
       <c r="R60" t="n">
         <v>11.91749538850425</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9494,23 +8619,13 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
@@ -9627,11 +8742,6 @@
       <c r="R61" t="n">
         <v>9.703490543791956</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9644,23 +8754,13 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>all</t>
@@ -9777,11 +8877,6 @@
       <c r="R62" t="n">
         <v>3.271963918848407</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9794,23 +8889,13 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>all</t>
@@ -9927,11 +9012,6 @@
       <c r="R63" t="n">
         <v>12.92943005255219</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9944,23 +9024,13 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>all</t>
@@ -10077,11 +9147,6 @@
       <c r="R64" t="n">
         <v>15.56735918806855</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10094,23 +9159,13 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>all</t>
@@ -10219,18 +9274,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3580</v>
+        <v>3629</v>
       </c>
       <c r="O65" t="n">
-        <v>3580</v>
+        <v>3629</v>
       </c>
       <c r="R65" t="n">
-        <v>13.14866631388085</v>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13.32863409303732</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -10244,23 +9294,13 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>all</t>
@@ -10377,11 +9417,6 @@
       <c r="R66" t="n">
         <v>6.943480072212192</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10394,23 +9429,13 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>all</t>
@@ -10527,11 +9552,6 @@
       <c r="R67" t="n">
         <v>12.89488420267113</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10544,23 +9564,13 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>all</t>
@@ -10677,11 +9687,6 @@
       <c r="R68" t="n">
         <v>61.36132897481954</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10694,23 +9699,13 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
@@ -10827,11 +9822,6 @@
       <c r="R69" t="n">
         <v>10.87210105617932</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10844,23 +9834,13 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
@@ -10977,11 +9957,6 @@
       <c r="R70" t="n">
         <v>10.22518358378077</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10994,23 +9969,13 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>all</t>
@@ -11127,11 +10092,6 @@
       <c r="R71" t="n">
         <v>4.477424310003082</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11144,23 +10104,13 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>all</t>
@@ -11277,11 +10227,6 @@
       <c r="R72" t="n">
         <v>12.31440851491728</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11294,23 +10239,13 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>all</t>
@@ -11427,11 +10362,6 @@
       <c r="R73" t="n">
         <v>16.76236393901988</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11444,23 +10374,13 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>all</t>
@@ -11569,18 +10489,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3378</v>
+        <v>3444</v>
       </c>
       <c r="O74" t="n">
-        <v>3378</v>
+        <v>3444</v>
       </c>
       <c r="R74" t="n">
-        <v>12.40675832633785</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12.64916390642616</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -11594,23 +10509,13 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>all</t>
@@ -11727,11 +10632,6 @@
       <c r="R75" t="n">
         <v>5.513940057344977</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11744,23 +10644,13 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
@@ -11877,11 +10767,6 @@
       <c r="R76" t="n">
         <v>12.13364774705727</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11894,23 +10779,13 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
@@ -12027,11 +10902,6 @@
       <c r="R77" t="n">
         <v>33.09792896217539</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12044,23 +10914,13 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
@@ -12177,11 +11037,6 @@
       <c r="R78" t="n">
         <v>11.29025878910929</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12194,23 +11049,13 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>all</t>
@@ -12327,11 +11172,6 @@
       <c r="R79" t="n">
         <v>8.607935159815446</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12344,23 +11184,13 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
@@ -12477,11 +11307,6 @@
       <c r="R80" t="n">
         <v>5.510676073849948</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12494,23 +11319,13 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>all</t>
@@ -12627,11 +11442,6 @@
       <c r="R81" t="n">
         <v>11.40585397068388</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12644,23 +11454,13 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>all</t>
@@ -12777,11 +11577,6 @@
       <c r="R82" t="n">
         <v>14.98600552544359</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12794,22 +11589,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13030,7 +11815,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66325</v>
+        <v>66440</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3629</v>
+        <v>3614</v>
       </c>
       <c r="O65" t="n">
-        <v>3629</v>
+        <v>3614</v>
       </c>
       <c r="R65" t="n">
-        <v>13.32863409303732</v>
+        <v>13.27354191574452</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -10489,13 +10489,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3444</v>
+        <v>3452</v>
       </c>
       <c r="O74" t="n">
-        <v>3444</v>
+        <v>3452</v>
       </c>
       <c r="R74" t="n">
-        <v>12.64916390642616</v>
+        <v>12.67854640098232</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66440</v>
+        <v>66433</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="O65" t="n">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="R65" t="n">
-        <v>13.27354191574452</v>
+        <v>13.269869103925</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -10489,13 +10489,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="O74" t="n">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="R74" t="n">
-        <v>12.67854640098232</v>
+        <v>12.68221921280183</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3613</v>
+        <v>3616</v>
       </c>
       <c r="O65" t="n">
-        <v>3613</v>
+        <v>3616</v>
       </c>
       <c r="R65" t="n">
-        <v>13.269869103925</v>
+        <v>13.28088753938356</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -10489,13 +10489,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="O74" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="R74" t="n">
-        <v>12.68221921280183</v>
+        <v>12.68589202462135</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -11632,6 +11632,141 @@
         </is>
       </c>
       <c r="BC82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>gonococcal-infection</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D150</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Gonococcal infection</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>淋球菌感染</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>2452</v>
+      </c>
+      <c r="O83" t="n">
+        <v>2452</v>
+      </c>
+      <c r="R83" t="n">
+        <v>9.005734581462525</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -11670,7 +11805,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11888,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -11763,7 +11898,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -11815,7 +11950,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66433</v>
+        <v>68889</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -10489,13 +10489,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="O74" t="n">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="R74" t="n">
-        <v>12.68589202462135</v>
+        <v>12.68221921280183</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68889</v>
+        <v>68888</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d150/2026-2029.xlsx
+++ b/diseases/d150/2026-2029.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>14.11828863423407</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,13 +788,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>8.577240089203297</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,13 +938,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
@@ -1041,6 +1071,11 @@
       <c r="R4" t="n">
         <v>13.86373060072514</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1053,13 +1088,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
@@ -1176,6 +1221,11 @@
       <c r="R5" t="n">
         <v>73.63359476978344</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1188,13 +1238,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1311,6 +1371,11 @@
       <c r="R6" t="n">
         <v>11.53418413331844</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1323,13 +1388,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
@@ -1446,6 +1521,11 @@
       <c r="R7" t="n">
         <v>10.22518358378077</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1458,13 +1538,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
@@ -1581,6 +1671,11 @@
       <c r="R8" t="n">
         <v>3.96079842807965</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1593,13 +1688,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
@@ -1716,6 +1821,11 @@
       <c r="R9" t="n">
         <v>12.88749676589527</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1728,13 +1838,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
@@ -1851,6 +1971,11 @@
       <c r="R10" t="n">
         <v>19.41075284653362</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1863,13 +1988,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>all</t>
@@ -1989,6 +2124,11 @@
       <c r="R11" t="n">
         <v>13.21844973845173</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2001,13 +2141,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>all</t>
@@ -2124,6 +2274,11 @@
       <c r="R12" t="n">
         <v>7.556140078583856</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2136,13 +2291,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2259,6 +2424,11 @@
       <c r="R13" t="n">
         <v>12.43352877502637</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2271,13 +2441,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2394,6 +2574,11 @@
       <c r="R14" t="n">
         <v>82.18699214203102</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2406,13 +2591,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2529,6 +2724,11 @@
       <c r="R15" t="n">
         <v>11.30768202798137</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2541,13 +2741,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2664,6 +2874,11 @@
       <c r="R16" t="n">
         <v>11.58158548775169</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2676,13 +2891,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2799,6 +3024,11 @@
       <c r="R17" t="n">
         <v>2.410920782309352</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2811,13 +3041,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -2934,6 +3174,11 @@
       <c r="R18" t="n">
         <v>13.2089852969317</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2946,13 +3191,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -3069,6 +3324,11 @@
       <c r="R19" t="n">
         <v>14.63073384272833</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3081,13 +3341,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -3207,6 +3477,11 @@
       <c r="R20" t="n">
         <v>14.56269886439597</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3219,13 +3494,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3342,6 +3627,11 @@
       <c r="R21" t="n">
         <v>7.964580082831633</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3354,13 +3644,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3477,6 +3777,11 @@
       <c r="R22" t="n">
         <v>14.16361162869423</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3489,13 +3794,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3612,6 +3927,11 @@
       <c r="R23" t="n">
         <v>76.60868950795651</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3624,13 +3944,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3747,6 +4077,11 @@
       <c r="R24" t="n">
         <v>11.69099328316718</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3759,13 +4094,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -3882,6 +4227,11 @@
       <c r="R25" t="n">
         <v>11.21640035975952</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3894,13 +4244,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -4017,6 +4377,11 @@
       <c r="R26" t="n">
         <v>4.305215682695271</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4029,13 +4394,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -4152,6 +4527,11 @@
       <c r="R27" t="n">
         <v>13.99173998119432</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4164,13 +4544,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -4287,6 +4677,11 @@
       <c r="R28" t="n">
         <v>19.28156314372806</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4299,13 +4694,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4422,6 +4827,11 @@
       <c r="R29" t="n">
         <v>13.88690148960433</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4434,13 +4844,23 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4557,6 +4977,11 @@
       <c r="R30" t="n">
         <v>6.126600063716641</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4569,13 +4994,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>all</t>
@@ -4692,6 +5127,11 @@
       <c r="R31" t="n">
         <v>13.32163797324254</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4704,13 +5144,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>all</t>
@@ -4827,6 +5277,11 @@
       <c r="R32" t="n">
         <v>77.35246319249978</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4839,13 +5294,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -4962,6 +5427,11 @@
       <c r="R33" t="n">
         <v>11.56903061106261</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4974,13 +5444,23 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -5097,6 +5577,11 @@
       <c r="R34" t="n">
         <v>11.73809339974833</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5109,13 +5594,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -5232,6 +5727,11 @@
       <c r="R35" t="n">
         <v>1.89429490038592</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5244,13 +5744,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -5367,6 +5877,11 @@
       <c r="R36" t="n">
         <v>13.36274068134043</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5379,13 +5894,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5502,6 +6027,11 @@
       <c r="R37" t="n">
         <v>17.18223047313791</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5514,13 +6044,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5637,6 +6177,11 @@
       <c r="R38" t="n">
         <v>13.45718250672051</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5649,13 +6194,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -5772,6 +6327,11 @@
       <c r="R39" t="n">
         <v>6.330820065840528</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5784,13 +6344,23 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -5907,6 +6477,11 @@
       <c r="R40" t="n">
         <v>14.03673888609192</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5919,13 +6494,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -6042,6 +6627,11 @@
       <c r="R41" t="n">
         <v>75.49302898114162</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6054,13 +6644,23 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -6177,6 +6777,11 @@
       <c r="R42" t="n">
         <v>10.92437077279556</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6189,13 +6794,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -6312,6 +6927,11 @@
       <c r="R43" t="n">
         <v>10.38169149577742</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6324,13 +6944,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>all</t>
@@ -6447,6 +7077,11 @@
       <c r="R44" t="n">
         <v>3.271963918848407</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6459,13 +7094,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>all</t>
@@ -6582,6 +7227,11 @@
       <c r="R45" t="n">
         <v>12.73374138148654</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6594,13 +7244,23 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>all</t>
@@ -6717,6 +7377,11 @@
       <c r="R46" t="n">
         <v>14.9537080997422</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6729,13 +7394,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>all</t>
@@ -6852,6 +7527,11 @@
       <c r="R47" t="n">
         <v>13.35801658759348</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6864,13 +7544,23 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>all</t>
@@ -6987,6 +7677,11 @@
       <c r="R48" t="n">
         <v>5.922380061592753</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6999,13 +7694,23 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>all</t>
@@ -7122,6 +7827,11 @@
       <c r="R49" t="n">
         <v>12.95255363112673</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7134,13 +7844,23 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>all</t>
@@ -7257,6 +7977,11 @@
       <c r="R50" t="n">
         <v>73.63359476978344</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7269,13 +7994,23 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
@@ -7392,6 +8127,11 @@
       <c r="R51" t="n">
         <v>11.41222146121387</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7404,13 +8144,23 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>all</t>
@@ -7527,6 +8277,11 @@
       <c r="R52" t="n">
         <v>10.85121523176735</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7539,13 +8294,23 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>all</t>
@@ -7662,6 +8427,11 @@
       <c r="R53" t="n">
         <v>4.477424310003082</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7674,13 +8444,23 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>all</t>
@@ -7797,6 +8577,11 @@
       <c r="R54" t="n">
         <v>12.92943005255219</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7809,13 +8594,23 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -7932,6 +8727,11 @@
       <c r="R55" t="n">
         <v>15.37357463386023</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7944,13 +8744,23 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -8067,6 +8877,11 @@
       <c r="R56" t="n">
         <v>13.74366182864305</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8079,13 +8894,23 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -8202,6 +9027,11 @@
       <c r="R57" t="n">
         <v>5.718160059468865</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8214,13 +9044,23 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -8337,6 +9177,11 @@
       <c r="R58" t="n">
         <v>13.97906945763633</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8349,13 +9194,23 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>all</t>
@@ -8472,6 +9327,11 @@
       <c r="R59" t="n">
         <v>76.23680266568489</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8484,13 +9344,23 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>all</t>
@@ -8607,6 +9477,11 @@
       <c r="R60" t="n">
         <v>11.91749538850425</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8619,13 +9494,23 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
@@ -8742,6 +9627,11 @@
       <c r="R61" t="n">
         <v>9.703490543791956</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8754,13 +9644,23 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>all</t>
@@ -8877,6 +9777,11 @@
       <c r="R62" t="n">
         <v>3.271963918848407</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8889,13 +9794,23 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>all</t>
@@ -9012,6 +9927,11 @@
       <c r="R63" t="n">
         <v>12.92943005255219</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9024,13 +9944,23 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>all</t>
@@ -9147,6 +10077,11 @@
       <c r="R64" t="n">
         <v>15.56735918806855</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9159,13 +10094,23 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>all</t>
@@ -9282,6 +10227,11 @@
       <c r="R65" t="n">
         <v>13.28088753938356</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9294,13 +10244,23 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>all</t>
@@ -9417,6 +10377,11 @@
       <c r="R66" t="n">
         <v>6.943480072212192</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9429,13 +10394,23 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>all</t>
@@ -9552,6 +10527,11 @@
       <c r="R67" t="n">
         <v>12.89488420267113</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9564,13 +10544,23 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>all</t>
@@ -9687,6 +10677,11 @@
       <c r="R68" t="n">
         <v>61.36132897481954</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9699,13 +10694,23 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
@@ -9822,6 +10827,11 @@
       <c r="R69" t="n">
         <v>10.87210105617932</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9834,13 +10844,23 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
@@ -9957,6 +10977,11 @@
       <c r="R70" t="n">
         <v>10.22518358378077</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9969,13 +10994,23 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>all</t>
@@ -10092,6 +11127,11 @@
       <c r="R71" t="n">
         <v>4.477424310003082</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10104,13 +11144,23 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>all</t>
@@ -10227,6 +11277,11 @@
       <c r="R72" t="n">
         <v>12.31440851491728</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10239,13 +11294,23 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>all</t>
@@ -10362,6 +11427,11 @@
       <c r="R73" t="n">
         <v>16.76236393901988</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10374,13 +11444,23 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>all</t>
@@ -10489,13 +11569,18 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="O74" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="R74" t="n">
-        <v>12.68221921280183</v>
+        <v>12.68589202462135</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -10509,13 +11594,23 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>all</t>
@@ -10632,6 +11727,11 @@
       <c r="R75" t="n">
         <v>5.513940057344977</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10644,13 +11744,23 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
@@ -10767,6 +11877,11 @@
       <c r="R76" t="n">
         <v>12.13364774705727</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10779,13 +11894,23 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
@@ -10902,6 +12027,11 @@
       <c r="R77" t="n">
         <v>33.09792896217539</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10914,13 +12044,23 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
@@ -11037,6 +12177,11 @@
       <c r="R78" t="n">
         <v>11.29025878910929</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11049,13 +12194,23 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>all</t>
@@ -11172,6 +12327,11 @@
       <c r="R79" t="n">
         <v>8.607935159815446</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11184,13 +12344,23 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
@@ -11307,6 +12477,11 @@
       <c r="R80" t="n">
         <v>5.510676073849948</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11319,13 +12494,23 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>all</t>
@@ -11442,6 +12627,11 @@
       <c r="R81" t="n">
         <v>11.40585397068388</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11454,13 +12644,23 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>all</t>
@@ -11577,6 +12777,11 @@
       <c r="R82" t="n">
         <v>14.98600552544359</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11589,13 +12794,23 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>all</t>
@@ -11712,6 +12927,11 @@
       <c r="R83" t="n">
         <v>9.005734581462525</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11724,12 +12944,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -11950,7 +13180,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68888</v>
+        <v>68889</v>
       </c>
     </row>
     <row r="16">
